--- a/bandi_estratti_totale.xlsx
+++ b/bandi_estratti_totale.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G162"/>
+  <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,76 +1304,76 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prova gratuita di 7 giorni per DEIPLUS Premium</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Data non specificata</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0€</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Prova gratuita</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>javascript:apri()</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://deiplus.build.it/index.php</t>
+          <t>https://myaccount.ericsson.net/xpra/#/home</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Abbonamento annuale DEIPLUS</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Data non specificata</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>390€</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Abbonamento annuale</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.build.it/deiplus-premium/</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://myaccount.ericsson.net/xpra/#/home</t>
+          <t>https://ericsson-supplier.ivalua.com/page.aspx/en/usr/login?ReturnUrl=%2fpage.aspx%2fit%2fbpm%2fprocess_manage_extranet%2f38751%3fuid%3d9e333fac-17b6-4a92-adc1-e091d290f4ab</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1447,7 +1447,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://ericsson-supplier.ivalua.com/page.aspx/en/usr/login?ReturnUrl=%2fpage.aspx%2fit%2fbpm%2fprocess_manage_extranet%2f38751%3fuid%3d9e333fac-17b6-4a92-adc1-e091d290f4ab</t>
+          <t>https://ericsson-supplier.ivalua.com/page.aspx/en/ctn/content_browse/usr_guides_suppliers</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1484,7 +1484,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://ericsson-supplier.ivalua.com/page.aspx/en/ctn/content_browse/usr_guides_suppliers</t>
+          <t>https://fibermind.wildcard.it:55437/xmeweb-login/#/login</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1521,12 +1521,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://fibermind.wildcard.it:55437/xmeweb-login/#/login</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1563,32 +1563,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Accesso Fornitori</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/esop/guest/go/public/login/internal</t>
         </is>
       </c>
     </row>
@@ -1600,32 +1588,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Documenti</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/esop/guest/go/public/opportunity/current</t>
         </is>
       </c>
     </row>
@@ -1637,44 +1613,32 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Assistenza Fornitori</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/esop/common-host/public/browserenv/requirements.jsp</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://iliadportal.vittoriarms.eu/PortalWeb/</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1706,23 +1670,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://partner.indraweb.net</t>
+          <t>https://iliadportal.vittoriarms.eu/PortalWeb/</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_manual</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Licitazioni</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1737,13 +1717,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Procurement Quality Requirements (PQR)</t>
+          <t>Búsqueda documento</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>navurl://a0bf35d78666518ccda789884e36d725</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1758,60 +1742,52 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Política de proveedores</t>
+          <t>Notification from Purchaser</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>navurl://444654406b7b0c0cdc3d7f19ac92f621</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://service.ariba.com/Sourcing.aw/109555007/aw?awh=r&amp;awssk=bFAnjivL&amp;dard=1</t>
+          <t>https://partner.indraweb.net</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Shipping Notifications</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>navurl://2db41249c714b5c39246c621cb04e810</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.gruppoiren.it</t>
+          <t>https://service.ariba.com/Sourcing.aw/109555007/aw?awh=r&amp;awssk=bFAnjivL&amp;dard=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1843,12 +1819,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://irideos-app.my.site.com/POF/loginflow/lightningLoginFlow.apexp?retURL=%2FPOF%2F_ui%2Fsystem%2Fsecurity%2FChangePassword%3FretURL%3D%252FPOF%252Fapex%252FCommunitiesLanding%26fromFrontdoor%3D1%26setupid%3DChangePassword&amp;sparkID=LoginFlowFornitori</t>
+          <t>https://portaleacquisti.gruppoiren.it</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>failed_manual</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1880,7 +1856,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://imprese.istat.it/</t>
+          <t>https://irideos-app.my.site.com/POF/loginflow/lightningLoginFlow.apexp?retURL=%2FPOF%2F_ui%2Fsystem%2Fsecurity%2FChangePassword%3FretURL%3D%252FPOF%252Fapex%252FCommunitiesLanding%26fromFrontdoor%3D1%26setupid%3DChangePassword&amp;sparkID=LoginFlowFornitori</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1917,7 +1893,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://service.ariba.com/Sourcing.aw/109555016/aw?awh=r&amp;awssk=lNqqA4RH&amp;dard=1&amp;ancdc=1</t>
+          <t>https://imprese.istat.it/</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1954,7 +1930,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://platform.application.prd.supplyon.com/logon/logonServlet</t>
+          <t>https://service.ariba.com/Sourcing.aw/109555016/aw?awh=r&amp;awssk=lNqqA4RH&amp;dard=1&amp;ancdc=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1991,7 +1967,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://service.ariba.com/Sourcing.aw/109555016/aw?awh=r&amp;awssk=lNqqA4RH&amp;dard=1&amp;ancdc=1</t>
+          <t>https://platform.application.prd.supplyon.com/logon/logonServlet</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2065,33 +2041,37 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/</t>
+          <t>https://service.ariba.com/Sourcing.aw/109555016/aw?awh=r&amp;awssk=lNqqA4RH&amp;dard=1&amp;ancdc=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SERVIZIO DI GESTIONE INTEGRATA DELLE MANUTENZIONI ORDINARIE DELLE OPERE EDILI, ELETTRICHE E IDRAULICHE DEL PATRIMONIO DI EDILIZIA RESIDENZIALE PUBBLICA DEL COMUNE DI MILANO, SUDDIVISA IN TRE LOTTI NON CUMULABILI</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>13/07/2026 14:00</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Servizi</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=308b8edb-7997-4b00-a03b-25966acb5ce7&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2088,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SERVIZIO DI VERIFICA PERIODICA E STRAORDINARIA DEGLI IMPIANTI DI MESSA A TERRA E DI PROTEZIONE CONTRO LE SCARICHE ATMOSFERICHE (LPS), AI SENSI E PER GLI EFFETTI DEL D.P.R. 22 OTTOBRE 2001, N. 462 E S.M.I SUDDIVISO IN 4 LOTTI DI CUI TRE CUMULABILI</t>
+          <t>SERVIZIO DI GESTIONE INTEGRATA DELLE MANUTENZIONI ORDINARIE DELLE OPERE EDILI, ELETTRICHE E IDRAULICHE DEL PATRIMONIO DI EDILIZIA RESIDENZIALE PUBBLICA DEL COMUNE DI MILANO, SUDDIVISA IN TRE LOTTI NON CUMULABILI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2124,7 +2104,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=a00128a0-700c-4fd7-b3ca-32468fa15950&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=308b8edb-7997-4b00-a03b-25966acb5ce7&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2121,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SERVIZIO DI RACCOLTA, TRASPORTO E SMALTIMENTO DEI RIFIUTI PRODOTTI DALL’ATTIVITA’ DI MANUTENZIONE DEL VERDE URBANO DELLA CITTA’ DI MILANO</t>
+          <t>SERVIZIO DI VERIFICA PERIODICA E STRAORDINARIA DEGLI IMPIANTI DI MESSA A TERRA E DI PROTEZIONE CONTRO LE SCARICHE ATMOSFERICHE (LPS), AI SENSI E PER GLI EFFETTI DEL D.P.R. 22 OTTOBRE 2001, N. 462 E S.M.I SUDDIVISO IN 4 LOTTI DI CUI TRE CUMULABILI</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>29/06/2026 14:00</t>
+          <t>13/07/2026 14:00</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -2157,7 +2137,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=589d7108-3a41-43c9-8692-b9c048f681f4&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=a00128a0-700c-4fd7-b3ca-32468fa15950&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2154,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SERVIZIO DI SOLLECITO TELEFONICO DEI CREDITI VANTATI DA MM S.P.A. NEI CONFRONTI DEGLI UTENTI RELATIVAMENTE A FATTURE INERENTI ALLA FORNITURA DEL SERVIZIO IDRICO INTEGRATO</t>
+          <t>SERVIZIO DI RACCOLTA, TRASPORTO E SMALTIMENTO DEI RIFIUTI PRODOTTI DALL’ATTIVITA’ DI MANUTENZIONE DEL VERDE URBANO DELLA CITTA’ DI MILANO</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2190,7 +2170,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=832ba171-9f95-492e-b716-d7ec01427ff7&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=589d7108-3a41-43c9-8692-b9c048f681f4&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2187,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SERVIZIO DI MANUTENZIONE DEI DISPOSITIVI DI ANCORAGGIO POSTI IN COPERTURA SUI FABBRICATI E.R.P. DI PROPRIETÀ DEL COMUNE DI MILANO IN GESTIONE A MM. S.p.A. FINALIZZATO ALL’OTTENIMENTO DEL RAPPORTO DI CONTROLLO DI MANUTENZIONE</t>
+          <t>SERVIZIO DI SOLLECITO TELEFONICO DEI CREDITI VANTATI DA MM S.P.A. NEI CONFRONTI DEGLI UTENTI RELATIVAMENTE A FATTURE INERENTI ALLA FORNITURA DEL SERVIZIO IDRICO INTEGRATO</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>25/06/2026 14:00</t>
+          <t>29/06/2026 14:00</t>
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
@@ -2223,7 +2203,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=f2ed335c-9de3-4dea-b6f3-029c528e5d09&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=832ba171-9f95-492e-b716-d7ec01427ff7&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
@@ -2240,12 +2220,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SERVIZIO DI MANUTENZIONE ORDINARIA E STRAORDINARIA GRUPPI DI POMPAGGIO CENTRALI ACQUEDOTTO COMPRESA LA FORNITURA DI NUOVI MOTORI ELETTRICI</t>
+          <t>SERVIZIO DI MANUTENZIONE DEI DISPOSITIVI DI ANCORAGGIO POSTI IN COPERTURA SUI FABBRICATI E.R.P. DI PROPRIETÀ DEL COMUNE DI MILANO IN GESTIONE A MM. S.p.A. FINALIZZATO ALL’OTTENIMENTO DEL RAPPORTO DI CONTROLLO DI MANUTENZIONE</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22/06/2026 14:00</t>
+          <t>25/06/2026 14:00</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -2256,7 +2236,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=14679b31-0497-4d3a-b10d-7af8339dd9cb&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=f2ed335c-9de3-4dea-b6f3-029c528e5d09&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
@@ -2273,12 +2253,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SERVIZIO DI COLTIVAZIONE, FORNITURA ED IMPIANTO DI ALBERI E ALTRE PIANTE PER IL VERDE URBANO ATTRAVERSO UN PROGRAMMA DI COLTIVAZIONE AD ELEVATO STANDARD DI QUALITA’.</t>
+          <t>SERVIZIO DI MANUTENZIONE ORDINARIA E STRAORDINARIA GRUPPI DI POMPAGGIO CENTRALI ACQUEDOTTO COMPRESA LA FORNITURA DI NUOVI MOTORI ELETTRICI</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22/06/2026 13:00</t>
+          <t>22/06/2026 14:00</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
@@ -2289,7 +2269,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=f7b278e6-691f-4953-9919-b4d22d83182e&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=14679b31-0497-4d3a-b10d-7af8339dd9cb&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
@@ -2306,12 +2286,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SERVIZIO DI MANUTENZIONE ORDINARIA E STRAORDINARIA ALLESTIMENTI CAMION SPURGHI DI PROPRIETÀ MM</t>
+          <t>SERVIZIO DI COLTIVAZIONE, FORNITURA ED IMPIANTO DI ALBERI E ALTRE PIANTE PER IL VERDE URBANO ATTRAVERSO UN PROGRAMMA DI COLTIVAZIONE AD ELEVATO STANDARD DI QUALITA’.</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>19/06/2026 14:00</t>
+          <t>22/06/2026 13:00</t>
         </is>
       </c>
       <c r="E58" t="inlineStr"/>
@@ -2322,44 +2302,40 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=9c23e7ec-260b-41f1-b45f-b6c159f8b51b&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=f7b278e6-691f-4953-9919-b4d22d83182e&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://service.ariba.com/Sourcing.aw/109521010/aw?awh=r&amp;awssk=xNf5p0Ij&amp;dard=1&amp;ancdc=1#b0</t>
+          <t>https://mm.pro-q.it/</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>SERVIZIO DI MANUTENZIONE ORDINARIA E STRAORDINARIA ALLESTIMENTI CAMION SPURGHI DI PROPRIETÀ MM</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>19/06/2026 14:00</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://mm.pro-q.it/Gare/RicercaGare/ButtonLoadingPage.aspx?idGara=9c23e7ec-260b-41f1-b45f-b6c159f8b51b&amp;buttonName=btnDettaglio&amp;FiltroPianificate=fHx8fDEwfDA=</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2416,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://procurement.openfiber.it/web/login.html</t>
+          <t>https://service.ariba.com/Sourcing.aw/109521010/aw?awh=r&amp;awssk=xNf5p0Ij&amp;dard=1&amp;ancdc=1#b0</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>failed_mfa</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2477,12 +2453,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.openes.io/it</t>
+          <t>https://procurement.openfiber.it/web/login.html</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>failed_mfa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2514,7 +2490,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://opnet.4buyer.it/portal</t>
+          <t>https://www.openes.io/it</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2588,7 +2564,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://opnet.4buyer.it/Portal/</t>
+          <t>https://opnet.4buyer.it/portal</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2625,7 +2601,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://ceit.vittoriarms.eu/</t>
+          <t>https://opnet.4buyer.it/Portal/</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2662,7 +2638,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://erm.valtellina.com/ERM</t>
+          <t>https://ceit.vittoriarms.eu/</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2699,12 +2675,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://sielte.operations.eu.dynamics.com/</t>
+          <t>https://erm.valtellina.com/ERM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2773,12 +2749,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>app.sikuro.it/login</t>
+          <t>https://sielte.operations.eu.dynamics.com/</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>failed_manual</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2847,37 +2823,37 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.arca.regione.lombardia.it/wps/portal/ARCA/Home/e-procurement/piattaforma-sintel</t>
+          <t>app.sikuro.it/login</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bando di gara per il servizio di supporto alla progettazione di infrastrutture digitali</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2023-12-31</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>100000</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Servizi di consulenza progetti IT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.ariaspa.it/wps/portal/Aria/Home/bandi/bando-1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2894,29 +2870,13 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Avviso per l'affidamento di incarichi per la gestione dell'innovazione tecnologica</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>50000</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Servizi di consulenza innovazione</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.ariaspa.it/wps/portal/Aria/Home/bandi/bando-2</t>
-        </is>
-      </c>
+          <t>Bando per l’affidamento della fornitura di strisce reattive per glicemia e chetonemia relativi sistemi di rilevazione e servizi connessi</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2931,29 +2891,13 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bando di Gara per i Servizi di Ingegneria</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2023-12-01</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>€ 500.000</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Servizi di ingegneria</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.ariaspa.it/dettaglioBando/12345</t>
-        </is>
-      </c>
+          <t>Consultazione di mercato nell’ambito di di ecotomografi cardiologici multidisciplinari senologici</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2968,219 +2912,123 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bando di Gara per la Fornitura di Materiali</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2024-01-15</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>€ 200.000</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Forniture</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.ariaspa.it/dettaglioBando/12346</t>
-        </is>
-      </c>
+          <t>Bando per la fornitura di servizi di manutenzione degli immobili e degli impianti (“Facility Management”) a favore degli Enti del S.S.R.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://sourcing-sirti.app.jaggaer.com</t>
+          <t>https://www.arca.regione.lombardia.it/wps/portal/ARCA/Home/e-procurement/piattaforma-sintel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Bando per la fornitura di vaccini antinfluenzali e anti pneumococco per la campagna di prevenzione stagionale e prodotti contro RSV</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://sourcing-sirti.app.jaggaer.com</t>
+          <t>https://www.arca.regione.lombardia.it/wps/portal/ARCA/Home/e-procurement/piattaforma-sintel</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Convenzione per la fornitura di farmaci</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://sourcing-sirti.app.jaggaer.com</t>
+          <t>https://www.arca.regione.lombardia.it/wps/portal/ARCA/Home/e-procurement/piattaforma-sintel</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Convenzione per la fornitura di soluzioni infusionali</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://site-fornitori.appspot.com/</t>
+          <t>https://www.arca.regione.lombardia.it/wps/portal/ARCA/Home/e-procurement/piattaforma-sintel</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Convenzione per la fornitura di farmaci</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://site-fornitori.appspot.com/</t>
+          <t>https://www.arca.regione.lombardia.it/wps/portal/ARCA/Home/e-procurement/piattaforma-sintel</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Convenzione per la fornitura di farmaci</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://saas.hrzucchetti.it/hrpsoleto</t>
+          <t>https://www.arca.regione.lombardia.it/wps/portal/ARCA/Home/e-procurement/piattaforma-sintel</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3217,7 +3065,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://albofornitori-sgs.sorgenia.it/fornitori/login.php?redir=</t>
+          <t>https://sourcing-sirti.app.jaggaer.com</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3254,7 +3102,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://supplier.telebit.it/esop/tle-host/public/telebit/web/login.jst?VISITORID=65ba8057-e568-4480-9e8a-b34b33df427e</t>
+          <t>https://sourcing-sirti.app.jaggaer.com</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3291,12 +3139,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://supplier.telebit.it</t>
+          <t>https://sourcing-sirti.app.jaggaer.com</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3328,12 +3176,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.vegaformazione.it/area-utenti.php</t>
+          <t>https://site-fornitori.appspot.com/</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>failed_manual</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3365,12 +3213,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://vetropack.vittoriarms.eu/PortalWeb/?url=%2FEmployeesPortal%2FPortalConfigRecovery&amp;p=aI8kXjAr1QbyFo4CixNapgweeo7C6BSO2WvJ_FUAuwX3m4F-30aPXlAcheN1Dx7iR7Q-efXPNQzvYaLZrGOFQsxBJwn-Flc6S51QXVj-MARBG5g3s9xv6M9ocLmtQlIBa3fvS2ofHpJBmOEqukqecqprLI3Gjf13NlpUTNeX6cNmiGCzYaidW1aq39sSR1o7q8NPfgIKc4iz5a6bZxwQ1L97SPOcRHFFTCKNhjsEshkwj7XtyXNQFQ2</t>
+          <t>https://site-fornitori.appspot.com/</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>failed_captcha</t>
+          <t>failed_manual</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3402,7 +3250,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://ndso.net.vodafone.it/QF/Account/Login.aspx</t>
+          <t>https://saas.hrzucchetti.it/hrpsoleto</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3439,7 +3287,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>https://nog.wind.it/windnogws/home/browse.action</t>
+          <t>https://albofornitori-sgs.sorgenia.it/fornitori/login.php?redir=</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3476,7 +3324,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://egwh.fa.em2.oraclecloud.com</t>
+          <t>https://supplier.telebit.it/esop/tle-host/public/telebit/web/login.jst?VISITORID=65ba8057-e568-4480-9e8a-b34b33df427e</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3513,12 +3361,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://egwh.fa.em2.oraclecloud.com</t>
+          <t>https://supplier.telebit.it</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3550,7 +3398,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>https://wind3privacy.azurewebsites.net/reg/login</t>
+          <t>https://www.vegaformazione.it/area-utenti.php</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3560,187 +3408,219 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Bando di Garanzia Giovani</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-11-15</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>€ 1.500.000</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Lavoro e occupazione</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.example.com/bando-garanzia-giovani</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://ethicscompliancehub-bip.accenture.com/businessintermediary/#/main/BusinessIntermediary</t>
+          <t>https://www.vegaformazione.it/area-utenti.php</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Bando per Progetti di Sviluppo Sostenibile</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-12-31</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>€ 500.000</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ambiente</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.example.com/bando-sviluppo-sostenibile</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it</t>
+          <t>https://vetropack.vittoriarms.eu/PortalWeb/?url=%2FEmployeesPortal%2FPortalConfigRecovery&amp;p=aI8kXjAr1QbyFo4CixNapgweeo7C6BSO2WvJ_FUAuwX3m4F-30aPXlAcheN1Dx7iR7Q-efXPNQzvYaLZrGOFQsxBJwn-Flc6S51QXVj-MARBG5g3s9xv6M9ocLmtQlIBa3fvS2ofHpJBmOEqukqecqprLI3Gjf13NlpUTNeX6cNmiGCzYaidW1aq39sSR1o7q8NPfgIKc4iz5a6bZxwQ1L97SPOcRHFFTCKNhjsEshkwj7XtyXNQFQ2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_captcha</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avviso ambito eDistribuzione</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025-02-18</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it/news/news/2025/02/avviso-ambito-e-distribuzione</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it</t>
+          <t>https://ndso.net.vodafone.it/QF/Account/Login.aspx</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cambia il Regolamento del Programma Sviluppo Fornitori di Enel</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it/news/news/2025/02/Cambia_il_Regolamento_del_Programma_Sviluppo_Fornitori_di_Enel</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it</t>
+          <t>https://nog.wind.it/windnogws/home/browse.action</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>WeBUY | Fermo delle attività su tutti i Gruppi Merceologici</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025-07-21</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it/news/news/2025/07/webuy-fermo-attivita-gruppi-merceologici</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it</t>
+          <t>https://egwh.fa.em2.oraclecloud.com</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Supplier Performance Management</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://globalprocurement.enel.com/it/news/news/2026/01/Supplier-Performance-Management</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://enispace.eni.com/it_IT/home.page</t>
+          <t>https://egwh.fa.em2.oraclecloud.com</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3777,12 +3657,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>https://enispace.eni.com/it_IT/home.page</t>
+          <t>https://wind3privacy.azurewebsites.net/reg/login</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3814,7 +3694,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://www.tecocse.it/cantieri/login.asp</t>
+          <t>https://ethicscompliancehub-bip.accenture.com/businessintermediary/#/main/BusinessIntermediary</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3851,229 +3731,173 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://renovit-supplier.ivalua.app/page.aspx/it/usr/login</t>
+          <t>https://globalprocurement.enel.com/it</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Supplier Performance Management</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>07 January 2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://globalprocurement.enel.com/it/news/news/2026/01/Supplier-Performance-Management</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://alfagest.lemainformatica.it/web/amadori/</t>
+          <t>https://globalprocurement.enel.com/it</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>WeBUY | Fermo delle attività su tutti i Gruppi Merceologici</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>21 July 2025</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://globalprocurement.enel.com/it/news/news/2025/07/webuy-fermo-attivita-gruppi-merceologici</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://suppliers.telecomitalia.it/tamtamy/user/login.action</t>
+          <t>https://globalprocurement.enel.com/it</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Cambia il Regolamento del Programma Sviluppo Fornitori di Enel</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>27 February 2025</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://globalprocurement.enel.com/it/news/news/2025/02/Cambia_il_Regolamento_del_Programma_Sviluppo_Fornitori_di_Enel</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://service.ariba.com/Sourcing.aw/109521010/aw?awh=r&amp;awssk=xNf5p0Ij&amp;dard=1&amp;ancdc=1#b0</t>
+          <t>https://globalprocurement.enel.com/it</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Avviso ambito eDistribuzione</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>18 February 2025</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://globalprocurement.enel.com/it/news/news/2025/02/avviso-ambito-e-distribuzione</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://e-procurement.engie.it</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Accesso ai Servizi Digitali Eni</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>CYBER SECURITY</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>eprocurement.gruppofs.it</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>AI Observatory</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>OPPORTUNITA' DI BUSINESS</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4083,22 +3907,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bandi e Avvisi in corso</t>
+          <t>Energia di Filiera</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>/esop/guest/go/public/opportunity/current?customLoginPage=/web/login.html</t>
-        </is>
-      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4108,96 +3932,72 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bandi e Avvisi scaduti ed Esiti di gara</t>
+          <t>Attenzione alle iniziative fraudolente in corso</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr"/>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>/esop/guest/go/public/opportunity/past?customLoginPage=/web/login.html</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://procurement-gruppoacea.app.jaggaer.com/</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Eni Supply Chain Awards 2025, scopri i finalisti per ogni categoria</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://sun.my.site.com/vendor/s/login</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Safety Tech: innovazione tecnologica e sicurezza</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>OPPORTUNITÀ DI BUSINESS</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>https://www.gruppohera.it/gruppo/fornitori</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4207,34 +4007,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bando di Gara per la fornitura di materiale idraulico</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2023-11-30</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>50,000€</t>
-        </is>
-      </c>
+          <t>Sustainable Supply Chain Finance</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Forniture</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.gruppohera.it/gruppo/fornitori/bandi/id-bando-001</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://www.gruppohera.it/gruppo/fornitori</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4244,34 +4032,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bando per servizio di manutenzione stradale</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2023-12-15</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>100,000€</t>
-        </is>
-      </c>
+          <t>Supportiamo lo sviluppo sostenibile delle imprese della filiera dell’energia</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Servizi</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.gruppohera.it/gruppo/fornitori/bandi/id-bando-002</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://www.gruppohera.it/gruppo/fornitori</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4281,289 +4057,197 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Appalto per ristrutturazione edifici pubblici</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2024-01-10</t>
-        </is>
-      </c>
+          <t>Open-es, l’iniziativa per la sostenibilità dell’intero ecosistema</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Edilizia</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.gruppohera.it/gruppo/fornitori/bandi/id-bando-003</t>
-        </is>
-      </c>
+          <t>SOSTENIBILITÀ</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://service.ariba.com/Authenticator.aw/ad/ssoIDP</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Incontri con il mercato</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>https://service.ariba.com/Authenticator.aw/ad/ssoIDP</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Il Programma dedicato alla filiera per la decarbonizzazione dei trasporti</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://uniportal.huawei.com/uniportal1/login-pc.html?redirect=https%3A%2F%2Fapp.huawei.com%2Fiscp%2Fesupplier%2Fportal%2F%23!%2Fportal%2Fiscp.esupplier.index%2Fiscp.esupplier.srm.selectNew.index</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Accesso ai Servizi Digitali Eni</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>CYBER SECURITY</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://condomini.baslab.it/auth/login</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>AI Observatory</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>OPPORTUNITA' DI BUSINESS</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://eprocurement.raiway.it/PortaleAppalti/it/homepage.wp</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Energia di Filiera</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://eprocurement.raiway.it/PortaleAppalti/it/homepage.wp</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Attenzione alle iniziative fraudolente in corso</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
       <c r="F119" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://www.edison.it/it/diventa-fornitore</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Eni Supply Chain Awards 2025, scopri i finalisti per ogni categoria</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4573,22 +4257,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Piattaforma Unica della Trasparenza</t>
+          <t>Safety Tech: innovazione tecnologica e sicurezza</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://put.anticorruzione.it</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>OPPORTUNITÀ DI BUSINESS</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4598,22 +4282,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Piattaforma Contratti Pubblici</t>
+          <t>Sustainable Supply Chain Finance</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.anticorruzione.it/-/piattaforma-contratti-pubblici</t>
-        </is>
-      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4623,22 +4307,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Portale dei pagamenti</t>
+          <t>Supportiamo lo sviluppo sostenibile delle imprese della filiera dell’energia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.anticorruzione.it/-/portale-dei-pagamenti-di-anac</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4648,22 +4332,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Whistleblowing</t>
+          <t>Open-es, l’iniziativa per la sostenibilità dell’intero ecosistema</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.anticorruzione.it/-/whistleblowing</t>
-        </is>
-      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SOSTENIBILITÀ</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4673,22 +4357,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Contact center</t>
+          <t>Incontri con il mercato</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>http://supportcenter.anticorruzione.it/</t>
-        </is>
-      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4698,22 +4382,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Digitalizzazione Contratti Pubblici</t>
+          <t>Il Programma dedicato alla filiera per la decarbonizzazione dei trasporti</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.anticorruzione.it/-/digitalizzazione-contratti-pubblici</t>
-        </is>
-      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>NEWS</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4723,47 +4407,59 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Registrazione utenti</t>
+          <t>Accesso ai Servizi Digitali Eni</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.anticorruzione.it/-/servizio-di-registrazione-e-profilazione-utenti</t>
-        </is>
-      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>CYBER SECURITY</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/per-le-imprese</t>
+          <t>https://enispace.eni.com/it_IT/home.page</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pubblicità a Valore Legale</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.anticorruzione.it/-/pubblicit%C3%A0-a-valore-legale-pvl-</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://saas.hrzucchetti.it/hrprunup/jsp/home.jsp</t>
+          <t>https://www.tecocse.it/cantieri/login.asp</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4800,7 +4496,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://supplier.coupahost.com/sessions/new</t>
+          <t>https://renovit-supplier.ivalua.app/page.aspx/it/usr/login</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4837,7 +4533,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://atlantefotg.my.site.com/vendorportal/s/</t>
+          <t>https://alfagest.lemainformatica.it/web/amadori/</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4874,7 +4570,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://autostrade.bravosolution.com/web/login.html</t>
+          <t>https://suppliers.telecomitalia.it/tamtamy/user/login.action</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4911,37 +4607,49 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://autostrade.bravosolution.com/web/login.html</t>
+          <t>https://service.ariba.com/Sourcing.aw/109521010/aw?awh=r&amp;awssk=xNf5p0Ij&amp;dard=1&amp;ancdc=1#b0</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bandi e Avvisi Pubblici e Privati</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr"/>
-      <c r="F133" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>/esop/guest/go/public/opportunity/current</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://ingate.invitalia.it</t>
+          <t>https://e-procurement.engie.it</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4973,7 +4681,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://www.openes.io/it</t>
+          <t>eprocurement.gruppofs.it</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -5010,86 +4718,62 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://www.openes.io/it</t>
+          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Bandi e Avvisi in corso</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/esop/guest/go/public/opportunity/current?customLoginPage=/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Autostrade BAW</t>
+          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Bandi e Avvisi scaduti ed Esiti di gara</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>/esop/guest/go/public/opportunity/past?customLoginPage=/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://a4mobility-appalti.maggiolicloud.it/PortaleAppalti/it/ppcommon_area_personale.wp?redirectflag=1</t>
+          <t>https://procurement-gruppoacea.app.jaggaer.com/</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>failed_captcha</t>
+          <t>failed_creds</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -5121,7 +4805,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>https://webuy.enel.com/</t>
+          <t>https://sun.my.site.com/vendor/s/login</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5158,44 +4842,44 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>https://new.sikuro.it/</t>
+          <t>https://www.gruppohera.it/gruppo/fornitori</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Bando per fornitura di servizi energetici</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>500000</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CPV 09300000-2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.gruppohera.it/gruppo/bandi/bando-energia</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>upq.terna.it</t>
+          <t>https://service.ariba.com/Authenticator.aw/ad/ssoIDP</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5232,7 +4916,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>https://suppliers.telecomitalia.it/tamtamy/user/login.action</t>
+          <t>https://service.ariba.com/Authenticator.aw/ad/ssoIDP</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5269,7 +4953,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>https://supplier.coupahost.com/sessions/new</t>
+          <t>https://uniportal.huawei.com/uniportal1/login-pc.html?redirect=https%3A%2F%2Fapp.huawei.com%2Fiscp%2Fesupplier%2Fportal%2F%23!%2Fportal%2Fiscp.esupplier.index%2Fiscp.esupplier.srm.selectNew.index</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5306,7 +4990,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>https://iliadportal.vittoriarms.eu</t>
+          <t>https://condomini.baslab.it/auth/login</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5343,12 +5027,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://eprocurement.fieramilano.it/ngp421/loginprocess</t>
+          <t>https://eprocurement.raiway.it/PortaleAppalti/it/homepage.wp</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -5380,7 +5064,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://iliad.diviteldatacenter.it/#login</t>
+          <t>https://eprocurement.raiway.it/PortaleAppalti/it/homepage.wp</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5417,12 +5101,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://fastweb.risk.coupahost.com/Dashboard/Home</t>
+          <t>https://www.edison.it/it/diventa-fornitore</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>failed_creds</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5454,12 +5138,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://www2.autostrade.it/</t>
+          <t>https://www.anticorruzione.it/per-le-imprese</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5491,12 +5175,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://fastweb.risk.coupahost.com/Dashboard/Home</t>
+          <t>https://saas.hrzucchetti.it/hrprunup/jsp/home.jsp</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>failed_creds</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5528,7 +5212,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://imprese.istat.it/</t>
+          <t>https://supplier.coupahost.com/sessions/new</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5565,32 +5249,44 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://atlantefotg.my.site.com/vendorportal/s/</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bandi di Gara</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/neg/project</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5600,7 +5296,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RdI</t>
+          <t>Accesso Fornitori</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
@@ -5608,14 +5304,14 @@
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/neg/rfi</t>
+          <t>https://autostrade.bravosolution.com/esop/guest/go/public/login/internal</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5625,7 +5321,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RdO</t>
+          <t>Documenti</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
@@ -5633,14 +5329,14 @@
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/neg/rfq</t>
+          <t>https://autostrade.bravosolution.com/esop/guest/go/public/opportunity/current</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5650,7 +5346,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Aste</t>
+          <t>Assistenza Fornitori</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
@@ -5658,39 +5354,51 @@
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/neg/auction</t>
+          <t>https://autostrade.bravosolution.com/esop/common-host/public/browserenv/requirements.jsp</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Contratti</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/neg/contract</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://ingate.invitalia.it</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5700,122 +5408,182 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Opportunità Pubblicate</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/opportunity</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://www.openes.io/it</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Profilo Azienda</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/profile/corporate</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://www.openes.io/it</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Mie Categorie</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr"/>
-      <c r="F158" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/profile/category/list</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>Autostrade BAW</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Valutazioni</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr"/>
-      <c r="F159" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/profile/assessments</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://a4mobility-appalti.maggiolicloud.it/PortaleAppalti/it/ppcommon_area_personale.wp?redirectflag=1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_captcha</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Gestisci Utenti</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it/esop/guest/go/profile/user</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://webuy.enel.com/</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5825,50 +5593,556 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Trasparency</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr"/>
-      <c r="F161" t="inlineStr"/>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it#fk</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
+          <t>https://new.sikuro.it/</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>failed_error</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>upq.terna.it</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>failed_error</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://suppliers.telecomitalia.it/tamtamy/user/login.action</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>failed_error</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://supplier.coupahost.com/sessions/new</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>failed_error</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://iliadportal.vittoriarms.eu</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>failed_manual</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://eprocurement.fieramilano.it/ngp421/loginprocess</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://iliad.diviteldatacenter.it/#login</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>failed_error</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://fastweb.risk.coupahost.com/Dashboard/Home</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>failed_creds</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://www2.autostrade.it/</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://fastweb.risk.coupahost.com/Dashboard/Home</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>failed_creds</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://imprese.istat.it/</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Indagine trimestrale su posti vacanti e ore lavorate (Edizione 2026): avvio posticipato e nuova piattaforma di acquisizione dati</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>01.04.2026</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://imprese.istat.it/</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Indagine trimestrale su posti vacanti e ore lavorate (Edizione 2026): nuova piattaforma di acquisizione dati e sospensione dell’accesso fino al 31 marzo 2026</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>15.03.2026</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://imprese.istat.it/</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Censimento permanente delle unità economiche: al via la fase conclusiva della Rilevazione multiscopo qualitativa sulle imprese. Anno 2025</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>16.02.2026</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>https://portaleacquisti.terna.it</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>failed_manual</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
           <t>www.anticorruzione.it</t>
         </is>
       </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>failed_error</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Nessun bando estratto o login fallito</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>failed_error</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Nessun bando estratto o login fallito</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/bandi_estratti_totale.xlsx
+++ b/bandi_estratti_totale.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,17 +466,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://fornitori.cellnextelecom.it/albo/login</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>success</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CELLNEXTELECOM</t>
+          <t>AUTOSTRADE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -513,17 +513,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://fastweb.risk.coupahost.com/Account/Login</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>failed_creds</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>AUTOSTRADE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://fastweb.risk.coupahost.com/Account/Login</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>AUTOSTRADE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -607,17 +607,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://fastweb.risk.coupahost.com/Account/Login</t>
+          <t>https://eprocurement.raiway.it/PortaleAppalti/it/homepage.wp</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>failed_creds</t>
+          <t>failed_error</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>RAIWAY</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -654,7 +654,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://supplier.coupahost.com/sessions/new</t>
+          <t>https://www.edison.it/it/diventa-fornitore</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SUPPLIER</t>
+          <t>EDISON</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -701,17 +701,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://fastweb.coupahost.com/sessions/supplier_login</t>
+          <t>https://www.anticorruzione.it/per-le-imprese</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>ANTICORRUZIONE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -748,7 +748,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://fastweb.coupahost.com/sessions/supplier_login</t>
+          <t>https://atlantefotg.my.site.com/vendorportal/s/</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>ATLANTEFOTG</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -795,7 +795,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://fastweb.coupahost.com/sessions/supplier_login</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>AUTOSTRADE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -842,27 +842,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://fastweb.coupahost.com/sessions/supplier_login</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Gara europea a procedura aperta per il Servizio di raccolta, trasporto, consegna alle sale conta e contazione dei valori depositati presso le stazioni autostradali o altri siti ubicati nel territorio di competenza di ogni Direzione di Tronco di Autostrade</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/06/2026 12:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -882,34 +882,34 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://fastweb.coupahost.com/sessions/supplier_login</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>COE_Fornitura di Cloruro di Calcio per le Direzioni di Tronco di ASPI</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10/06/2026 12:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Forniture</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -929,14 +929,14 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://deiplus.build.it/index.php</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DEIPLUS</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>RDA 458591 - CTA RIQUALIFICA BS T1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15/06/2026 23:59</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -966,7 +966,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -976,34 +976,34 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://myaccount.ericsson.net/xpra/#/home</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>failed_captcha</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MYACCOUNT</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Servizio di prove di laboratorio e indagini in sito, indagini geognostiche e rilievi topografici</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/06/2026 12:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
@@ -1035,22 +1035,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AUTOSTRADE</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>GARA EUROPEA A PROCEDURA APERTA PER IL SERVIZIO MANUTENTIVO DEGLI IMPIANTI DI ESAZIONE DI PEDAGGIO, DI VIABILITA', DI INFRASTRUTTURE ED ELETTRICI, COMPRENSIVO DI FORNITURA ACCESSORIA DI PARTI DI RICAMBIO.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17/06/2026 18:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1060,7 +1060,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
@@ -1082,22 +1082,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AUTOSTRADE</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>APN_Servizio cablaggio impianti di esazione svincolo Maddaloni - A30</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/06/2026 12:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
@@ -1129,22 +1129,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>failed_error</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AUTOSTRADE</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>903832_S.U. - Supporto idrodemolizioni nell'ambito degli interventi in somma urgenza del ponte di scolo Calcarata km. 23+991 nei tratti di competenza della Direzione 3^ Tronco Bologna</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/06/2026 23:00</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1164,34 +1164,34 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://a4mobility-appalti.maggiolicloud.it/PortaleAppalti/it/ppcommon_area_personale.wp?redirectflag=1</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A4MOBILITY-APPALTI</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>S.U. - DT 5 - SERVIZI DI INGEGNERIA Direzione lavori e CSE per interventi su op. Idraul. N. 241</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30/06/2026 23:59</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1211,34 +1211,34 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www2.autostrade.it/</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>failed_manual</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WWW2</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>Procedura aperta ex art. 71 D.Lgs. 36/2023_Acquisto licenze Microsoft MPSA 2026-29</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>01/07/2026 12:00</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Forniture</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1258,34 +1258,34 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://fastweb.risk.coupahost.com/Dashboard/Home</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>failed_creds</t>
+          <t>success</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FASTWEB</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>PROCEDURA APERTA PER L’AFFIDAMENTO DELLA FORNITURA DI ROUTER CISCO DI BACKBONE PER I TRONCHI E DI ROUTER CISCO GEOGRAFICI PER LE STAZIONI, AREE DI SERVIZIO, SHELTER E GALLERIE SITUATI SULLE TRATTE AUTOSTRADALI DI COMPETENZA DI AUTOSTRADE PER L’ITALIA S.P.A</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>01/07/2026 12:00</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Forniture</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1305,14 +1305,14 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://imprese.istat.it/</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1322,17 +1322,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>IMPRESE</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>ESE_PROCEDURA APERTA PER L’APPALTO DEI SERVIZI MECCANIZZATI DI SGOMBERO NEVE E TRATTAMENTO ANTIGHIACCIO DA ESEGUIRSI LUNGO LE TRATTE AUTOSTRADALI DI COMPETENZA DELLA DIREZIONE 8° TRONCO DI BARI  (A16 - P.N. CANDELA, P.N. CERIGNOLA, P.N. CANOSA)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>01/07/2026 16:00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1352,14 +1352,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://portaleacquisti.terna.it</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1369,17 +1369,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PORTALETERNA</t>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>ESE_GARA EUROPEA A PROCEDURA APERTA PER L’AFFIDAMENTO DI MANUTENZIONEORDINARIA PROGRAMMATA ED INTERVENTI STRAORDINARI DI RIPRISTINO FUNZIONALITÀ DEGLI IMPIANTI DI STOCCAGGIO CLORURI PER DISGELO STRADALE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>06/07/2026 16:00</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1399,30 +1399,34 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>www.anticorruzione.it</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>failed_error</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Nessun bando estratto o login fallito</t>
+          <t>TES_Servizio taratura e manutenzione delle apparecchiature PENETROMETRO e REOMETRO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>08/07/2026 18:00</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1442,7 +1446,1942 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Negoziata ai sensi dell’art. 76 comma 4 lett. b del D.lgs. 36/2023
+TES_Fornitura SUMMS 5 e manutenzione triennale WDM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10/07/2026 00:00</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Forniture</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TES_Fornitura n. 2 mezzi Ecodyn, misura della retroriflessione della segnaletica orizzontale e contratto di manutenzione</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10/07/2026 14:00</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>L.i.Fe srl- aff. diretto- prove su mat. da costruzione - Galleria Monte Mario - A1-tratta Casalecchio di Reno – Sasso Marconi</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>30/09/2026 00:00</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Affidamento diretto Speri S.p.A - VAL4- tratte di competenza DT2, DT5 e DT7</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>31/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>459056_ INCARICO DI SERVIZI DI INGEGNERIA PER INTERVENTO DI SOMMA URGENZA DI RIPRISTINO PONTE ADIGE KM 72+249 NEL TRATTO DI COMPETENZA DELLA DIREZIONE 3^ TRONCO DI BOLOGNA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>31/10/2026 12:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>904083 - DT03/TEC
+904083 - DT3 - Somma Urgenza Alluvione 18 e 19 Settembre 2024 - Ripristino treansitabilità A14 tra le progressive 92+000 e 118+000  e D14 (Diramazione Ravenna) - Rimozione Fanghi.</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>31/12/2026 14:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>451778 - DT03/TECNICA
+451778 - Intervento di Somma Urgenza per il ripristino dei gravi eventi alluvionali del 19 e 20 Ottobre 2024 - Pulizia Fabbricati. Ripristino delle funzionalità e della salubrità delle unità immobiliari di pertinenza DT3.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>31/12/2026 14:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>452833 - DT03/TEC
+452833 - Servizio di supporto al coordinatore per la sicurezza in fase di esecuzione per aspetti geotecnici e strutturali per l’intervento di somma urgenza di ripristino a seguito dei gravi eventi alluvionali del 18 e 19 settembre 2024.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>31/12/2026 14:00</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>904359 - DT03/Tecnica
+904359 - Somma Urgenza 18 e 19 Sett_2024 - A14 Intervento di ripristino Segnaletica Orizzontale.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>31/12/2026 18:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>456913_S.U. INTERVENTO DI SOMMA URGENZA DI RIPRISTINO A SEGUITO DEI GRAVI EVENTI ALLUVIONALI DEL 18 E 19 SETTEMBRE 2024_ SPURGO OPERE IDRAULICHE</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>31/12/2026 20:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>GST S.N.C. - Assistenza topografica nell'ambito del progetto A1 MILANO - NAPOLI Tratto Modena – Brennero (A22)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>24/02/2027 23:59</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Ing. Gilbo - Servizio di collaudo statico - Tunnel subportuale Genova</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>01/05/2027 23:59</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>446747 - DT3/TEC
+446747 - Somma Urgenza per il ripristino del Ponte Scolo Calcarata km 23+991 - A13 Bologna - Padova - Prove di Laboratorio</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>31/12/2027 14:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Aff. diretto - Ing. Caputo - Viadotto Paolo e Omero - Collaudo Statico - RdA 455916</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17/03/2028 12:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>904625 - DT3/TECNICA
+904625 - Intervento di somma urgenza a seguito dei gravi eventi alluvionali del 18 e 19 settembre 2024 - Ripristino smottamenti localizzati in A14. Fornitura e posa in opera palancole.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>31/12/2028 12:00</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ASA-DT3-TEC-462866 -SU RIPRISTINO GIUNTO LAMELLARE PONTE RENO - PE - DL - CSE</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>29/01/2029 15:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ASA-DT3-TEC-904930 - DT3-TEC - A1 SOMMA URGENZA GIUNTO LAMELLARE PONTE RENO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>29/01/2029 15:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>AERTECNO s.r.l. - Servizio di Servizio di assistenza topografica - Opere complementari di Pesaro - Altre bretelle</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>16/02/2030 23:29</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>DT3_somma urgenza per intervento di messa in sicurezza e ripristino delle condizioni di transitabilità dell’Autostrada A14 tra le progr. Km 92+000 e km 118+000 e la D14 a seguito degli eventi alluvionali del 18 e 19 settembre 2024</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23/05/2030 00:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Avvisi di gara procedure non telematiche (2017-2021) vecchio portale NGA</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>01/06/2030 00:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>DT3 - COD. APP. 021/BO/2024 SOMMA URGENZA 19-20 OTTOBRE 2024 - LAVORI FORNITURA E POSA PALANCOLE</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>04/06/2030 12:00</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>S.U.- INTERVENTI DI RISPRISTINO A SEGUITO DI ALLUVIONE 19 E 20 OTTOBRE 2024 - DT3 - COLLAUDO STATICO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21/08/2030 12:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Avviso istituzione Albo Fornitori</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>01/09/2030 00:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Altro</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>451161 DT3-RIPRISTINO IMP. CLIMATIZZAZIONE-SU/EVENTI ALLUVIONALI 18/19 SET.2024</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>10/11/2030 00:00</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>452711 DT3-SUPPORTO DL-SU/EVENTI ALLUVIONALI 18/19 SET.2024</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>10/11/2030 12:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SOMMA URGENZA DI RIPRISTINO PONTE ADIGE KM 72+249 - INSTALLAZIONE CANTIERIZZAZIONE, GUARDIANIA E SEGNALAMENTO ACCODAMENTI IN AMBITO AUTOSTRADALE - DT3</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>11/11/2030 09:00</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Avviso istituzione nuova sezione Albo Fornitori - Servizi di ingegneria</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>31/12/2030 00:00</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Altro</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ASA - DT3-TEC - 459054 - SU PONTE ADIGE KM 72+249 - FORNITURA MAT. SISTEMI PRECOMPRESSIONE</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>16/01/2031 14:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Forniture</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>904671 - SOMMA URGENZA PER RIPRISTINO SISTEMI DI PRECOMPRESSIONE PONTE ADIGE KM 72+249</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>26/01/2031 14:00</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>ASA - DT3-TEC - 456119 - SU OTT 2024  - Fornitura barriere New Jersey ET 100</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>30/01/2031 14:00</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Forniture</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ASA-DT3-TEC 453151 - CST PER SU EVENTI ALLUVIONALI DEL 19 E 20 OTTOBRE 2024</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>06/02/2031 15:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ASA - DT3-TEC - 459055 - SU PONTE ADIGE KM 72+249 - INDAGINI E PROVE DI LABORATORIO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>16/02/2031 14:00</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>904754_Intervento in somma urgenza per la messa in sicurezza del fabbricato e pensiline della stazione di Roma Ovest a seguito di incendio di un veicolo presente in pista</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>31/03/2031 23:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ARAN PROGETTI S.R.L. - Servizio di sorveglianza archeologica - Progetti speciali Liguria Lotto A e Lotto B</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>07/04/2031 23:59</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>ASA - DT3 - TEC - 905067 - A14 SU SETT. 2024_SEGNALETICA CANT. E NJ</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>14/04/2031 14:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ASA - DT3 - TEC - 904994 - SU OTTORE 2024 - PALANCOLE</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>17/04/2031 14:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lavori</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>443718 - DT03/TEC
+443718 - DT3 - Somma Urgenza Cavalcavia Occhiobello A13 - Installazione cantierizzazione, guardiania e regolazione dei flussi veicolari.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>31/12/2031 14:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>455277_S.U._Incarico di progettazione e  Coordinamento della Sicurezza in fase di progettazione nell'ambito degli interventi sull'OP. 241 km.624.728  N.- DT5</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>31/12/2035 12:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Servizi</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Istruzioni Fatturazione Elettronica</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>21/12/2099 12:00</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Altro</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Avviso pubblico Nuovo Regolamento Albo Fornitori 2021</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>31/12/2099 00:00</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Altro</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AUTOSTRADE PER L'ITALIA SPA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Nuovo Albo Fornitori del Gruppo Autostrade</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>31/12/2999 12:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Altro</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://autostrade.bravosolution.com/web/login.html</t>
         </is>
       </c>
     </row>

--- a/bandi_estratti_totale.xlsx
+++ b/bandi_estratti_totale.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,27 +466,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>eprocurement.gruppofs.it</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
-        </is>
-      </c>
+          <t>failed_error</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DAC.0186.2026_Fornitura di "PALI TE"</t>
+          <t>Nessun bando estratto o login fallito</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,17 +492,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fornitura</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fornitura di "PALI TE"</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -523,17 +519,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DAC.326.2026 - Servizio per interventi su chiamata e programmati per pulizia, rimozione detriti su pile dei ponti dei fiumi ricadenti nella giurisdizione della Direzione Operativa Infrastrutture Milano</t>
+          <t>DAC.0186.2026_Fornitura di "PALI TE"</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>15/06/2026 12:00</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -543,17 +539,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Servizi</t>
+          <t>Fornitura</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Servizio per interventi su chiamata e programmati per pulizia, rimozione detriti su pile dei ponti dei fiumi ricadenti nella giurisdizione della Direzione Operativa Infrastrutture Milano</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -570,17 +566,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DAC.0317.2026_GPA_Servizio di manutenzione attrezzature e macchinari dell’Officina Nazionale Mezzi d’Opera</t>
+          <t>DAC.326.2026 - Servizio per interventi su chiamata e programmati per pulizia, rimozione detriti su pile dei ponti dei fiumi ricadenti nella giurisdizione della Direzione Operativa Infrastrutture Milano</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>17/06/2026 12:00</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -595,12 +591,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Servizio di manutenzione attrezzature e macchinari dell’Officina Nazionale Mezzi d’Opera</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -617,17 +613,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DAC.0211.2026 - Key Management System</t>
+          <t>DAC.0317.2026_GPA_Servizio di manutenzione attrezzature e macchinari dell’Officina Nazionale Mezzi d’Opera</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18/06/2026 12:00</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -642,12 +638,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Key Management System</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -664,17 +660,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DAC.0010.2026 - GPA Multilotto Fornitura, in regime di Full Maintenance Service, dei Caricatori Strada Rotaia pesanti</t>
+          <t>DAC.0211.2026 - Key Management System</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>19/06/2026 12:00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -684,17 +680,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fornitura</t>
+          <t>Servizi</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Fornitura, in regime di Full Maintenance Service, dei Caricatori Strada Rotaia pesanti</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -711,17 +707,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DAC.0193.2026_Fornitura di Attrezzaggio TE</t>
+          <t>DAC.0010.2026 - GPA Multilotto Fornitura, in regime di Full Maintenance Service, dei Caricatori Strada Rotaia pesanti</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>22/06/2026 12:00</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -736,12 +732,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Fornitura di Attrezzaggio TE</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -758,17 +754,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DAC.0006.2026 - GPA Multilotto Fornitura, in regime di Full Maintenance Service, di Carri Tramoggia da 20 m3</t>
+          <t>DAC.0193.2026_Fornitura di Attrezzaggio TE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>22/06/2026 12:00</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -783,12 +779,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>GPA Multilotto Fornitura, in regime di Full Maintenance Service, di Carri Tramoggia da 20 m3</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -805,17 +801,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DAC.0008.2026 - Fornitura, in regime di Full Maintenance Service, di Stabilizzatrici da utilizzare per il mantenimento in efficienza dell’Infrastruttura Ferroviaria Nazionale</t>
+          <t>DAC.0006.2026 - GPA Multilotto Fornitura, in regime di Full Maintenance Service, di Carri Tramoggia da 20 m3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>23/06/2026 12:00</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -830,12 +826,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Fornitura, in regime di Full Maintenance Service, di Stabilizzatrici da utilizzare per il mantenimento in efficienza dell’Infrastruttura Ferroviaria Nazionale</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -852,17 +848,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DAC.0111.2026_Fornitura di SALDATURE ALLUMINOTERMICHE</t>
+          <t>DAC.0008.2026 - Fornitura, in regime di Full Maintenance Service, di Stabilizzatrici da utilizzare per il mantenimento in efficienza dell’Infrastruttura Ferroviaria Nazionale</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>26/06/2026 12:00</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -877,12 +873,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Fornitura di SALDATURE ALLUMINOTERMICHE</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -899,17 +895,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DAC.0374.2026 MDI_Isolatori per tirante a  terra per i sostegni di ormeggio tipo "LS-LSF-LSFP</t>
+          <t>DAC.0111.2026_Fornitura di SALDATURE ALLUMINOTERMICHE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>29/06/2026 12:00</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -924,12 +920,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Fornitura di isolatori per tirante a terra per i sostegni di ormeggio tipo "LS-LSF-LSFP".</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -946,17 +942,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DAC.0294.2026_Fornitura di MENSOLE IN ACCIAIO</t>
+          <t>DAC.0374.2026 MDI_Isolatori per tirante a  terra per i sostegni di ormeggio tipo "LS-LSF-LSFP</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>30/06/2026</t>
+          <t>30/06/2026 12:00</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -971,12 +967,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fornitura di mensole in acciaio.</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -993,17 +989,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DAC.0337.2026_AQ Indagini  Geognostiche, Geofisiche, Geotecniche e sui Materiali</t>
+          <t>DAC.0294.2026_Fornitura di MENSOLE IN ACCIAIO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>01/07/2026</t>
+          <t>30/06/2026 12:00</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1013,17 +1009,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lavori</t>
+          <t>Fornitura</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Indagini Geognostiche, Geofisiche, Geotecniche e sui Materiali</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -1040,17 +1036,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DAC.0332.2026 - FORNITURA DI AGHI GREZZI CON FORGIATURA (Componenti per AdD +- 200)</t>
+          <t>DAC.0337.2026_AQ Indagini  Geognostiche, Geofisiche, Geotecniche e sui Materiali</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>02/07/2026</t>
+          <t>01/07/2026 12:00</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1060,17 +1056,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fornitura</t>
+          <t>Lavori</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Fornitura di aghi grezzi con forgiatura (Componenti per AdD +- 200)</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -1087,17 +1083,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DAC.0254.2026 - FORNITURA DI BARRE DI COLLEGAMENTO AD U (Componenti per AdD +/- 200)</t>
+          <t>DAC.0332.2026 - FORNITURA DI AGHI GREZZI CON FORGIATURA (Componenti per AdD +- 200)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>03/07/2026</t>
+          <t>02/07/2026 12:00</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1112,12 +1108,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fornitura di barre di collegamento ad U (Componenti per AdD +/- 200)</t>
+          <t>Rete Ferroviaria Italiana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
@@ -1134,37 +1130,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RETE FERROVIARIA ITALIANA</t>
+          <t>ACQUISTIONLINERFI</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>DAC.0254.2026 - FORNITURA DI BARRE DI COLLEGAMENTO AD U (Componenti per AdD +/- 200)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>03/07/2026 12:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fornitura</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Rete Ferroviaria Italiana</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ACQUISTIONLINERFI</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>DAC.0366.2026 - GPA- Fornitura con posa nr. due macchine fresatrici ONA Pontassieve</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>07/07/2026</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>07/07/2026 12:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Fornitura</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Fornitura con posa nr. due macchine fresatrici ONA Pontassieve</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>https://www.acquistionlinerfi.it/web/error.html?_ncp=1753696951455.127431-1</t>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Rete Ferroviaria Italiana</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://www.acquistionlinerfi.it/esop/toolkit/opportunity/current/list.si?reset=true&amp;resetstored=true&amp;customLoginPage=%2Fweb%2Flogin.html&amp;_ncp=1781183967356.1684912-1#fh</t>
         </is>
       </c>
     </row>
